--- a/quality_surveys/013_pressure_injury_prevention_survey--quality_surveys.xlsx
+++ b/quality_surveys/013_pressure_injury_prevention_survey--quality_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Any other comments</t>
+          <t>Training Needs Comment Hint</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Any other comments</t>
+          <t>Barriers Comment Hint</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -805,7 +805,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Any other comments</t>
+          <t>Any other comments (4)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -823,7 +823,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>prevention_practices</t>
+          <t>prevention_practices_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>prevention_practices_comment</t>
+          <t>prevention_practices_comment_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Prevention Practices Comment 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -897,7 +897,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Using Compression Devices Comment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Using Foam Comment</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Using Other Comment</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Any other comments</t>
+          <t>Using Other 2 Hint</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Using Other 2 Comment</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Other (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>prevention_practices_choices</t>
+          <t>prevention_practices_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>prevention_practices_choices</t>
+          <t>prevention_practices_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>prevention_practices_choices</t>
+          <t>prevention_practices_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>prevention_practices_choices</t>
+          <t>prevention_practices_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
